--- a/Banc de test/banc_de_test.xlsx
+++ b/Banc de test/banc_de_test.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projet_capteur\2025-2026-4GP-NGUYEN-PHAN-GAMBOA\Banc de test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F9A346E-00A8-46A3-A4CC-85EAD2E040D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB966C08-C11B-477A-A7FA-A19C4D4F73E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D1397E9D-800F-410F-B2F5-486FD72217ED}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="46">
   <si>
     <t>Ro</t>
   </si>
@@ -174,6 +174,9 @@
   </si>
   <si>
     <t>FLEX</t>
+  </si>
+  <si>
+    <t>A</t>
   </si>
 </sst>
 </file>
@@ -328,7 +331,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -395,9 +398,6 @@
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -441,7 +441,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -454,10 +454,26 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="vi-VN"/>
-              <a:t>Tension </a:t>
+              <a:rPr lang="vi-VN" sz="1800" b="0">
+                <a:latin typeface="+mn-lt"/>
+              </a:rPr>
+              <a:t>S</a:t>
             </a:r>
-            <a:endParaRPr lang="en-US"/>
+            <a:r>
+              <a:rPr lang="en-US" sz="1800" b="0">
+                <a:latin typeface="+mn-lt"/>
+              </a:rPr>
+              <a:t>ensibilité du graphite sous </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="vi-VN" sz="1800" b="0">
+                <a:latin typeface="+mn-lt"/>
+              </a:rPr>
+              <a:t>tension</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US" sz="1800" b="0">
+              <a:latin typeface="+mn-lt"/>
+            </a:endParaRPr>
           </a:p>
         </c:rich>
       </c:tx>
@@ -465,8 +481,8 @@
         <c:manualLayout>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.41158631273179019"/>
-          <c:y val="1.5082956259426848E-2"/>
+          <c:x val="0.23126248784124193"/>
+          <c:y val="1.0219139665851521E-3"/>
         </c:manualLayout>
       </c:layout>
       <c:overlay val="0"/>
@@ -477,26 +493,6 @@
         </a:ln>
         <a:effectLst/>
       </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
@@ -505,62 +501,24 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="7.5096653341625727E-2"/>
-          <c:y val="9.6479831718484857E-2"/>
-          <c:w val="0.73010947158601891"/>
-          <c:h val="0.81778788612272701"/>
+          <c:x val="7.5252594367863759E-2"/>
+          <c:y val="7.1696338406424795E-2"/>
+          <c:w val="0.70738573538662775"/>
+          <c:h val="0.86123538961991963"/>
         </c:manualLayout>
       </c:layout>
       <c:scatterChart>
         <c:scatterStyle val="lineMarker"/>
         <c:varyColors val="0"/>
         <c:ser>
-          <c:idx val="2"/>
+          <c:idx val="5"/>
           <c:order val="0"/>
           <c:tx>
             <c:v>4B</c:v>
           </c:tx>
-          <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent3"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent3"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent3"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:trendline>
-            <c:spPr>
-              <a:ln w="19050" cap="rnd">
-                <a:solidFill>
-                  <a:schemeClr val="accent3"/>
-                </a:solidFill>
-                <a:prstDash val="sysDot"/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:trendlineType val="linear"/>
-            <c:dispRSqr val="0"/>
-            <c:dispEq val="0"/>
-          </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>Sheet1!$E$104:$E$109</c:f>
+              <c:f>Sheet1!$E$105:$E$110</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
@@ -568,26 +526,26 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.098901098901099E-2</c:v>
+                  <c:v>4.4247787610619468E-3</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.2345679012345678E-2</c:v>
+                  <c:v>4.9751243781094526E-3</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.4084507042253521E-2</c:v>
+                  <c:v>5.681818181818182E-3</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.6393442622950821E-2</c:v>
+                  <c:v>6.6225165562913916E-3</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.9607843137254902E-2</c:v>
+                  <c:v>7.9365079365079378E-3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet1!$D$104:$D$109</c:f>
+              <c:f>Sheet1!$D$105:$D$110</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
@@ -615,57 +573,19 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-5762-4F8B-83CA-379095BA17C3}"/>
+              <c16:uniqueId val="{00000014-6CF6-4809-8496-E10257614497}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
         <c:ser>
-          <c:idx val="3"/>
+          <c:idx val="6"/>
           <c:order val="1"/>
           <c:tx>
             <c:v>6B</c:v>
           </c:tx>
-          <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent4"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent4"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent4"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:trendline>
-            <c:spPr>
-              <a:ln w="19050" cap="rnd">
-                <a:solidFill>
-                  <a:schemeClr val="accent4"/>
-                </a:solidFill>
-                <a:prstDash val="sysDot"/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:trendlineType val="linear"/>
-            <c:dispRSqr val="0"/>
-            <c:dispEq val="0"/>
-          </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>Sheet1!$E$110:$E$115</c:f>
+              <c:f>Sheet1!$E$111:$E$116</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
@@ -673,26 +593,26 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.098901098901099E-2</c:v>
+                  <c:v>4.4247787610619468E-3</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.2345679012345678E-2</c:v>
+                  <c:v>4.9751243781094526E-3</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.4084507042253521E-2</c:v>
+                  <c:v>5.681818181818182E-3</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.6393442622950821E-2</c:v>
+                  <c:v>6.6225165562913916E-3</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.9607843137254902E-2</c:v>
+                  <c:v>7.9365079365079378E-3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet1!$D$110:$D$115</c:f>
+              <c:f>Sheet1!$D$111:$D$116</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
@@ -720,18 +640,18 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-5762-4F8B-83CA-379095BA17C3}"/>
+              <c16:uniqueId val="{00000015-6CF6-4809-8496-E10257614497}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
         <c:ser>
-          <c:idx val="4"/>
+          <c:idx val="7"/>
           <c:order val="2"/>
           <c:tx>
             <c:v>Flex sensor</c:v>
           </c:tx>
           <c:spPr>
-            <a:ln w="19050" cap="rnd">
+            <a:ln>
               <a:gradFill>
                 <a:gsLst>
                   <a:gs pos="0">
@@ -760,39 +680,8 @@
                 </a:gsLst>
                 <a:lin ang="5400000" scaled="1"/>
               </a:gradFill>
-              <a:round/>
             </a:ln>
-            <a:effectLst/>
           </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent5"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent5"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:trendline>
-            <c:spPr>
-              <a:ln w="19050" cap="rnd">
-                <a:solidFill>
-                  <a:schemeClr val="accent5"/>
-                </a:solidFill>
-                <a:prstDash val="sysDot"/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:trendlineType val="linear"/>
-            <c:dispRSqr val="0"/>
-            <c:dispEq val="0"/>
-          </c:trendline>
           <c:xVal>
             <c:numRef>
               <c:f>Sheet1!$E$39:$E$44</c:f>
@@ -803,19 +692,19 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.098901098901099E-2</c:v>
+                  <c:v>4.4247787610619468E-3</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.2345679012345678E-2</c:v>
+                  <c:v>4.9751243781094526E-3</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.4084507042253521E-2</c:v>
+                  <c:v>5.681818181818182E-3</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.6393442622950821E-2</c:v>
+                  <c:v>6.6225165562913916E-3</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.9607843137254902E-2</c:v>
+                  <c:v>7.9365079365079378E-3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -850,13 +739,147 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-068B-4D82-85AC-94482E4656A7}"/>
+              <c16:uniqueId val="{00000016-6CF6-4809-8496-E10257614497}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="8"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:v>HB</c:v>
+          </c:tx>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$E$93:$E$98</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4.4247787610619468E-3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4.9751243781094526E-3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5.681818181818182E-3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6.6225165562913916E-3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>7.9365079365079378E-3</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$D$93:$D$98</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.35639116143408311</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.43560577190116279</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.45982995135320492</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.53998033266532552</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.63478213250547288</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000017-6CF6-4809-8496-E10257614497}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="9"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:v>2B</c:v>
+          </c:tx>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$E$99:$E$104</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4.4247787610619468E-3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4.9751243781094526E-3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5.681818181818182E-3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6.6225165562913916E-3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>7.9365079365079378E-3</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$D$99:$D$104</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.23635897203469025</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.28073482279172374</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.33210816890404715</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.44451718628037595</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.51543595158028543</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000018-6CF6-4809-8496-E10257614497}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="0"/>
-          <c:order val="3"/>
+          <c:order val="5"/>
           <c:tx>
             <c:v>HB</c:v>
           </c:tx>
@@ -900,7 +923,7 @@
           </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>Sheet1!$E$92:$E$97</c:f>
+              <c:f>Sheet1!$E$2:$E$7</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
@@ -908,26 +931,26 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.098901098901099E-2</c:v>
+                  <c:v>4.4247787610619468E-3</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.2345679012345678E-2</c:v>
+                  <c:v>4.9751243781094526E-3</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.4084507042253521E-2</c:v>
+                  <c:v>5.681818181818182E-3</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.6393442622950821E-2</c:v>
+                  <c:v>6.6225165562913916E-3</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.9607843137254902E-2</c:v>
+                  <c:v>7.9365079365079378E-3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet1!$D$92:$D$97</c:f>
+              <c:f>Sheet1!$D$2:$D$7</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
@@ -935,19 +958,19 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.35639116143408311</c:v>
+                  <c:v>-0.65800238184169657</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.43560577190116279</c:v>
+                  <c:v>-0.66872047652620781</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.45982995135320492</c:v>
+                  <c:v>-0.67615287946199265</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.53998033266532552</c:v>
+                  <c:v>-0.69143803226504197</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.63478213250547288</c:v>
+                  <c:v>-0.70895944126813171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -955,15 +978,15 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-BC01-4CC0-86D9-AC29740FE3CA}"/>
+              <c16:uniqueId val="{00000007-6CF6-4809-8496-E10257614497}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="1"/>
-          <c:order val="4"/>
+          <c:order val="6"/>
           <c:tx>
-            <c:v>2B</c:v>
+            <c:v>Flex</c:v>
           </c:tx>
           <c:spPr>
             <a:ln w="19050" cap="rnd">
@@ -1005,7 +1028,7 @@
           </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>Sheet1!$E$98:$E$103</c:f>
+              <c:f>Sheet1!$E$32:$E$37</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
@@ -1013,26 +1036,26 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.098901098901099E-2</c:v>
+                  <c:v>4.4247787610619468E-3</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.2345679012345678E-2</c:v>
+                  <c:v>4.9751243781094526E-3</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.4084507042253521E-2</c:v>
+                  <c:v>5.681818181818182E-3</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.6393442622950821E-2</c:v>
+                  <c:v>6.6225165562913916E-3</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.9607843137254902E-2</c:v>
+                  <c:v>7.9365079365079378E-3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet1!$D$98:$D$103</c:f>
+              <c:f>Sheet1!$D$32:$D$37</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
@@ -1040,19 +1063,19 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.23635897203469025</c:v>
+                  <c:v>-0.54777911111111111</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.28073482279172374</c:v>
+                  <c:v>-0.57403955555555553</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.33210816890404715</c:v>
+                  <c:v>-0.59108799999999995</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.44451718628037595</c:v>
+                  <c:v>-0.639768</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.51543595158028543</c:v>
+                  <c:v>-0.69189199999999995</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1060,7 +1083,322 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-BC01-4CC0-86D9-AC29740FE3CA}"/>
+              <c16:uniqueId val="{0000000A-6CF6-4809-8496-E10257614497}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="7"/>
+          <c:tx>
+            <c:v>2B</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$E$9:$E$14</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4.4247787610619468E-3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4.9751243781094526E-3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5.681818181818182E-3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6.6225165562913916E-3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>7.9365079365079378E-3</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$D$9:$D$14</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-0.32892163223867499</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-0.36847616738523603</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-0.3826446844681079</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-0.41178303319266357</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-0.44518439543326527</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{0000000D-6CF6-4809-8496-E10257614497}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="8"/>
+          <c:tx>
+            <c:v>4B</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent4"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent4"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$E$15:$E$20</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4.4247787610619468E-3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4.9751243781094526E-3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5.681818181818182E-3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6.6225165562913916E-3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>7.9365079365079378E-3</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$D$15:$D$20</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-0.13326830767150816</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-0.14608820375417497</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-0.15738145527283678</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-0.18337322669157569</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-0.20799137197304662</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000010-6CF6-4809-8496-E10257614497}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="9"/>
+          <c:tx>
+            <c:v>6B</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent5"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent5"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$E$21:$E$26</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4.4247787610619468E-3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4.9751243781094526E-3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5.681818181818182E-3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6.6225165562913916E-3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>7.9365079365079378E-3</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$D$21:$D$26</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-7.1710237246169137E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-0.14279611579131113</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-0.16476442489084264</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-0.19644328739159103</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-0.20638373429797591</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000013-6CF6-4809-8496-E10257614497}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1072,11 +1410,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="376613184"/>
-        <c:axId val="376613664"/>
+        <c:axId val="1264351135"/>
+        <c:axId val="1264351615"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="376613184"/>
+        <c:axId val="1264351135"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1103,7 +1441,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:schemeClr val="tx1">
                         <a:lumMod val="65000"/>
@@ -1116,13 +1454,20 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="vi-VN"/>
+                  <a:rPr lang="en-US" sz="1400"/>
                   <a:t>Deformation</a:t>
                 </a:r>
-                <a:endParaRPr lang="en-US"/>
               </a:p>
             </c:rich>
           </c:tx>
+          <c:layout>
+            <c:manualLayout>
+              <c:xMode val="edge"/>
+              <c:yMode val="edge"/>
+              <c:x val="0.4041751729922663"/>
+              <c:y val="0.95024529001937585"/>
+            </c:manualLayout>
+          </c:layout>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -1131,26 +1476,6 @@
             </a:ln>
             <a:effectLst/>
           </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="65000"/>
-                      <a:lumOff val="35000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
@@ -1189,12 +1514,12 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="376613664"/>
+        <c:crossAx val="1264351615"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="376613664"/>
+        <c:axId val="1264351615"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1221,7 +1546,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:schemeClr val="tx1">
                         <a:lumMod val="65000"/>
@@ -1234,29 +1559,40 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                  <a:rPr lang="en-US" sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:sysClr>
+                    </a:solidFill>
                     <a:effectLst/>
                   </a:rPr>
                   <a:t>∆</a:t>
                 </a:r>
                 <a:r>
-                  <a:rPr lang="vi-VN" sz="1000" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                  <a:rPr lang="vi-VN" sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:sysClr>
+                    </a:solidFill>
                     <a:effectLst/>
                   </a:rPr>
                   <a:t>R/Ro</a:t>
                 </a:r>
-                <a:endParaRPr lang="en-US"/>
+                <a:endParaRPr lang="en-US" sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:sysClr>
+                  </a:solidFill>
+                </a:endParaRPr>
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout>
-            <c:manualLayout>
-              <c:xMode val="edge"/>
-              <c:yMode val="edge"/>
-              <c:x val="7.1186309979433295E-3"/>
-              <c:y val="0.43712868470924443"/>
-            </c:manualLayout>
-          </c:layout>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -1265,26 +1601,6 @@
             </a:ln>
             <a:effectLst/>
           </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="65000"/>
-                      <a:lumOff val="35000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
@@ -1323,30 +1639,13 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="376613184"/>
+        <c:crossAx val="1264351135"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
     </c:plotArea>
     <c:legend>
-      <c:legendPos val="b"/>
-      <c:layout>
-        <c:manualLayout>
-          <c:xMode val="edge"/>
-          <c:yMode val="edge"/>
-          <c:x val="0.80370920944663016"/>
-          <c:y val="0.26319937652272135"/>
-          <c:w val="0.19609685237761834"/>
-          <c:h val="0.38823504110259627"/>
-        </c:manualLayout>
-      </c:layout>
+      <c:legendPos val="r"/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -1379,29 +1678,8 @@
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
+    <c:extLst/>
   </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
   <c:txPr>
     <a:bodyPr/>
     <a:lstStyle/>
@@ -1629,19 +1907,19 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>3736144.75</c:v>
+                  <c:v>2239067</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>3704544.75</c:v>
+                  <c:v>2223423</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3612785.75</c:v>
+                  <c:v>2190271</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3554027.25</c:v>
+                  <c:v>2155526</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>3529409</c:v>
+                  <c:v>2140971</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1772,19 +2050,19 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>3529409</c:v>
+                  <c:v>2140971</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>3541676.5</c:v>
+                  <c:v>2157970</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3621334.25</c:v>
+                  <c:v>2220836</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3677869.75</c:v>
+                  <c:v>2231219</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>3700073</c:v>
+                  <c:v>2231219</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1915,19 +2193,19 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>3700073</c:v>
+                  <c:v>2231219</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>3669060.75</c:v>
+                  <c:v>2226016</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3634230.75</c:v>
+                  <c:v>2210544</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3578980.75</c:v>
+                  <c:v>2145802</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>3465349</c:v>
+                  <c:v>2133764</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2029,7 +2307,7 @@
           </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>Sheet1!$B$66:$B$70</c:f>
+              <c:f>Sheet1!$B$67:$B$71</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
@@ -2053,24 +2331,24 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet1!$C$66:$C$70</c:f>
+              <c:f>Sheet1!$C$67:$C$71</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>23867.4</c:v>
+                  <c:v>33307</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>24055.45</c:v>
+                  <c:v>32528</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>24244.9</c:v>
+                  <c:v>31519</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>24435.759999999998</c:v>
+                  <c:v>28463</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>24919.17</c:v>
+                  <c:v>27586</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2172,7 +2450,7 @@
           </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>Sheet1!$B$70:$B$74</c:f>
+              <c:f>Sheet1!$B$71:$B$75</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
@@ -2196,24 +2474,24 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet1!$C$70:$C$74</c:f>
+              <c:f>Sheet1!$C$71:$C$75</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>24919.17</c:v>
+                  <c:v>27586</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>24531.72</c:v>
+                  <c:v>30905</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>24340.15</c:v>
+                  <c:v>32019</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>24150</c:v>
+                  <c:v>32528</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>24055.45</c:v>
+                  <c:v>33705</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2315,7 +2593,7 @@
           </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>Sheet1!$B$74:$B$78</c:f>
+              <c:f>Sheet1!$B$75:$B$79</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
@@ -2339,24 +2617,24 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet1!$C$74:$C$78</c:f>
+              <c:f>Sheet1!$C$75:$C$79</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>24055.45</c:v>
+                  <c:v>33705</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>24150</c:v>
+                  <c:v>31768</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>24244.9</c:v>
+                  <c:v>30905</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>24531.72</c:v>
+                  <c:v>29484</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>24919.17</c:v>
+                  <c:v>28242</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2365,6 +2643,304 @@
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000006-A8F3-46D7-A5B5-C8C306160362}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="6"/>
+          <c:order val="6"/>
+          <c:tx>
+            <c:v>40-120/G 2</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="60000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="t"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$B$61:$B$65</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>80</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>120</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$C$61:$C$65</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>2133764</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2140971</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2220836</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2228614</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2231219</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-0F3E-49B5-937C-9A483CDA2EFF}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="7"/>
+          <c:order val="7"/>
+          <c:tx>
+            <c:v>40-120/F 2</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2">
+                    <a:lumMod val="60000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="t"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$B$79:$B$83</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>80</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>120</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$C$79:$C$83</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>28242</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>30905</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>31643</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>32272</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>33705</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-0F3E-49B5-937C-9A483CDA2EFF}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2775,10 +3351,10 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.16300946185534074"/>
-          <c:y val="0.16841086497720584"/>
-          <c:w val="0.63155920272149457"/>
-          <c:h val="0.63487531404329012"/>
+          <c:x val="6.9942958519506104E-2"/>
+          <c:y val="2.4452751166487336E-2"/>
+          <c:w val="0.91032930198401762"/>
+          <c:h val="0.93646274771806115"/>
         </c:manualLayout>
       </c:layout>
       <c:scatterChart>
@@ -2816,7 +3392,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Sheet1!$B$66:$B$70</c:f>
+              <c:f>Sheet1!$B$67:$B$71</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
@@ -2840,24 +3416,24 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet1!$C$66:$C$70</c:f>
+              <c:f>Sheet1!$C$67:$C$71</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>23867.4</c:v>
+                  <c:v>33307</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>24055.45</c:v>
+                  <c:v>32528</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>24244.9</c:v>
+                  <c:v>31519</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>24435.759999999998</c:v>
+                  <c:v>28463</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>24919.17</c:v>
+                  <c:v>27586</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2901,7 +3477,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Sheet1!$B$70:$B$74</c:f>
+              <c:f>Sheet1!$B$71:$B$75</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
@@ -2925,24 +3501,24 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet1!$C$70:$C$74</c:f>
+              <c:f>Sheet1!$C$71:$C$75</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>24919.17</c:v>
+                  <c:v>27586</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>24531.72</c:v>
+                  <c:v>30905</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>24340.15</c:v>
+                  <c:v>32019</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>24150</c:v>
+                  <c:v>32528</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>24055.45</c:v>
+                  <c:v>33705</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2986,7 +3562,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Sheet1!$B$74:$B$78</c:f>
+              <c:f>Sheet1!$B$75:$B$79</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
@@ -3010,24 +3586,24 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet1!$C$74:$C$78</c:f>
+              <c:f>Sheet1!$C$75:$C$79</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>24055.45</c:v>
+                  <c:v>33705</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>24150</c:v>
+                  <c:v>31768</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>24244.9</c:v>
+                  <c:v>30905</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>24531.72</c:v>
+                  <c:v>29484</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>24919.17</c:v>
+                  <c:v>28242</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3036,6 +3612,91 @@
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000002-A3AE-4042-8A06-65746F3C6982}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:v>40-120(2)</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent4"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$B$79:$B$83</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>80</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>120</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$C$79:$C$83</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>28242</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>30905</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>31643</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>32272</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>33705</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-8492-4D34-A54B-672459486C3A}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3519,19 +4180,19 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>3736144.75</c:v>
+                  <c:v>2239067</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>3704544.75</c:v>
+                  <c:v>2223423</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3612785.75</c:v>
+                  <c:v>2190271</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3554027.25</c:v>
+                  <c:v>2155526</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>3529409</c:v>
+                  <c:v>2140971</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3604,19 +4265,19 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>3529409</c:v>
+                  <c:v>2140971</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>3541676.5</c:v>
+                  <c:v>2157970</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3621334.25</c:v>
+                  <c:v>2220836</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3677869.75</c:v>
+                  <c:v>2231219</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>3700073</c:v>
+                  <c:v>2231219</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3689,19 +4350,19 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>3700073</c:v>
+                  <c:v>2231219</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>3669060.75</c:v>
+                  <c:v>2226016</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3634230.75</c:v>
+                  <c:v>2210544</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3578980.75</c:v>
+                  <c:v>2145802</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>3465349</c:v>
+                  <c:v>2133764</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3710,6 +4371,91 @@
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000002-5172-458C-8ABC-E15E9BE69B8A}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:v>40-120/2</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent4"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$B$61:$B$65</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>80</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>120</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$C$61:$C$65</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>2133764</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2140971</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2220836</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2228614</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2231219</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-8968-4041-82B9-5C5788982CD2}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4062,7 +4808,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -4075,8 +4821,12 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-US"/>
-              <a:t>Compression</a:t>
+              <a:rPr lang="vi-VN" sz="1800" b="0"/>
+              <a:t>S</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" sz="1800" b="0"/>
+              <a:t>ensibilité du graphite sous compression</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -4085,8 +4835,8 @@
         <c:manualLayout>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.43187163150980906"/>
-          <c:y val="6.5445026178010471E-3"/>
+          <c:x val="0.23126248784124193"/>
+          <c:y val="1.0219139665851521E-3"/>
         </c:manualLayout>
       </c:layout>
       <c:overlay val="0"/>
@@ -4102,7 +4852,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+            <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="65000"/>
@@ -4127,8 +4877,8 @@
           <c:yMode val="edge"/>
           <c:x val="7.5252594367863759E-2"/>
           <c:y val="7.1696338406424795E-2"/>
-          <c:w val="0.71794404547355661"/>
-          <c:h val="0.88332607285571096"/>
+          <c:w val="0.70738573538662775"/>
+          <c:h val="0.86123538961991963"/>
         </c:manualLayout>
       </c:layout>
       <c:scatterChart>
@@ -4188,19 +4938,19 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.098901098901099E-2</c:v>
+                  <c:v>4.4247787610619468E-3</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.2345679012345678E-2</c:v>
+                  <c:v>4.9751243781094526E-3</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.4084507042253521E-2</c:v>
+                  <c:v>5.681818181818182E-3</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.6393442622950821E-2</c:v>
+                  <c:v>6.6225165562913916E-3</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.9607843137254902E-2</c:v>
+                  <c:v>7.9365079365079378E-3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4293,19 +5043,19 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.098901098901099E-2</c:v>
+                  <c:v>4.4247787610619468E-3</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.2345679012345678E-2</c:v>
+                  <c:v>4.9751243781094526E-3</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.4084507042253521E-2</c:v>
+                  <c:v>5.681818181818182E-3</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.6393442622950821E-2</c:v>
+                  <c:v>6.6225165562913916E-3</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.9607843137254902E-2</c:v>
+                  <c:v>7.9365079365079378E-3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4398,19 +5148,19 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.098901098901099E-2</c:v>
+                  <c:v>4.4247787610619468E-3</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.2345679012345678E-2</c:v>
+                  <c:v>4.9751243781094526E-3</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.4084507042253521E-2</c:v>
+                  <c:v>5.681818181818182E-3</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.6393442622950821E-2</c:v>
+                  <c:v>6.6225165562913916E-3</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.9607843137254902E-2</c:v>
+                  <c:v>7.9365079365079378E-3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4503,19 +5253,19 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.098901098901099E-2</c:v>
+                  <c:v>4.4247787610619468E-3</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.2345679012345678E-2</c:v>
+                  <c:v>4.9751243781094526E-3</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.4084507042253521E-2</c:v>
+                  <c:v>5.681818181818182E-3</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.6393442622950821E-2</c:v>
+                  <c:v>6.6225165562913916E-3</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.9607843137254902E-2</c:v>
+                  <c:v>7.9365079365079378E-3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4608,19 +5358,19 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.098901098901099E-2</c:v>
+                  <c:v>4.4247787610619468E-3</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.2345679012345678E-2</c:v>
+                  <c:v>4.9751243781094526E-3</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.4084507042253521E-2</c:v>
+                  <c:v>5.681818181818182E-3</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.6393442622950821E-2</c:v>
+                  <c:v>6.6225165562913916E-3</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.9607843137254902E-2</c:v>
+                  <c:v>7.9365079365079378E-3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4698,7 +5448,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:schemeClr val="tx1">
                         <a:lumMod val="65000"/>
@@ -4711,7 +5461,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="en-US"/>
+                  <a:rPr lang="en-US" sz="1400"/>
                   <a:t>Deformation</a:t>
                 </a:r>
               </a:p>
@@ -4738,7 +5488,7 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
                     <a:schemeClr val="tx1">
                       <a:lumMod val="65000"/>
@@ -4823,7 +5573,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:schemeClr val="tx1">
                         <a:lumMod val="65000"/>
@@ -4836,7 +5586,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:rPr lang="en-US" sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:sysClr val="windowText" lastClr="000000">
                         <a:lumMod val="65000"/>
@@ -4848,7 +5598,7 @@
                   <a:t>∆</a:t>
                 </a:r>
                 <a:r>
-                  <a:rPr lang="vi-VN" sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:rPr lang="vi-VN" sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:sysClr val="windowText" lastClr="000000">
                         <a:lumMod val="65000"/>
@@ -4859,7 +5609,7 @@
                   </a:rPr>
                   <a:t>R/Ro</a:t>
                 </a:r>
-                <a:endParaRPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:endParaRPr lang="en-US" sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
                     <a:sysClr val="windowText" lastClr="000000">
                       <a:lumMod val="65000"/>
@@ -4883,7 +5633,7 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
                     <a:schemeClr val="tx1">
                       <a:lumMod val="65000"/>
@@ -5183,46 +5933,6 @@
 </cs:colorStyle>
 </file>
 
-<file path=xl/charts/colors5.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
-  <a:schemeClr val="accent1"/>
-  <a:schemeClr val="accent2"/>
-  <a:schemeClr val="accent3"/>
-  <a:schemeClr val="accent4"/>
-  <a:schemeClr val="accent5"/>
-  <a:schemeClr val="accent6"/>
-  <cs:variation/>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-    <a:lumOff val="20000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-    <a:lumOff val="40000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-    <a:lumOff val="30000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-    <a:lumOff val="50000"/>
-  </cs:variation>
-</cs:colorStyle>
-</file>
-
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
@@ -6772,522 +7482,6 @@
 </file>
 
 <file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="75000"/>
-          <a:lumOff val="25000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:prstDash val="sysDot"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
-<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -7843,16 +8037,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>222338</xdr:colOff>
-      <xdr:row>61</xdr:row>
-      <xdr:rowOff>9937</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>18422</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>64394</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>27</xdr:col>
-      <xdr:colOff>131488</xdr:colOff>
-      <xdr:row>87</xdr:row>
-      <xdr:rowOff>54758</xdr:rowOff>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>579549</xdr:colOff>
+      <xdr:row>86</xdr:row>
+      <xdr:rowOff>22560</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -7880,15 +8074,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>579120</xdr:colOff>
-      <xdr:row>79</xdr:row>
-      <xdr:rowOff>4795</xdr:rowOff>
+      <xdr:colOff>117627</xdr:colOff>
+      <xdr:row>86</xdr:row>
+      <xdr:rowOff>58454</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>308534</xdr:colOff>
-      <xdr:row>94</xdr:row>
-      <xdr:rowOff>172720</xdr:rowOff>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>10733</xdr:colOff>
+      <xdr:row>134</xdr:row>
+      <xdr:rowOff>53662</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -7915,16 +8109,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>599440</xdr:colOff>
-      <xdr:row>62</xdr:row>
-      <xdr:rowOff>235236</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>524312</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>74250</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>193427</xdr:colOff>
-      <xdr:row>78</xdr:row>
-      <xdr:rowOff>142240</xdr:rowOff>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>343436</xdr:colOff>
+      <xdr:row>90</xdr:row>
+      <xdr:rowOff>118056</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -7951,16 +8145,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>158052</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>221552</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>99786</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>25</xdr:col>
-      <xdr:colOff>233680</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>20321</xdr:rowOff>
+      <xdr:colOff>145143</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>145142</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -8305,7 +8499,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D325BECD-CEA4-4140-9D69-0F9C0C2F40A5}">
-  <dimension ref="A1:M115"/>
+  <dimension ref="A1:M116"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.6640625" customWidth="1"/>
@@ -8380,13 +8574,13 @@
       </c>
       <c r="E3" s="3">
         <f>$G$3/(2*B3+$G$3)</f>
-        <v>1.098901098901099E-2</v>
+        <v>4.4247787610619468E-3</v>
       </c>
       <c r="F3" s="17">
         <v>2280378.25</v>
       </c>
       <c r="G3" s="3">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="H3" s="14">
         <v>1.02</v>
@@ -8412,10 +8606,12 @@
       </c>
       <c r="E4" s="3">
         <f t="shared" ref="E4:E7" si="1">$G$3/(2*B4+$G$3)</f>
-        <v>1.2345679012345678E-2</v>
+        <v>4.9751243781094526E-3</v>
       </c>
       <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
+      <c r="G4" s="3">
+        <v>0.2</v>
+      </c>
       <c r="H4" s="14" t="s">
         <v>12</v>
       </c>
@@ -8442,10 +8638,12 @@
       </c>
       <c r="E5" s="3">
         <f t="shared" si="1"/>
-        <v>1.4084507042253521E-2</v>
+        <v>5.681818181818182E-3</v>
       </c>
       <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
+      <c r="G5" s="3">
+        <v>0.2</v>
+      </c>
       <c r="H5" s="14" t="s">
         <v>14</v>
       </c>
@@ -8470,10 +8668,12 @@
       </c>
       <c r="E6" s="3">
         <f t="shared" si="1"/>
-        <v>1.6393442622950821E-2</v>
+        <v>6.6225165562913916E-3</v>
       </c>
       <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
+      <c r="G6" s="3">
+        <v>0.2</v>
+      </c>
       <c r="H6" s="14" t="s">
         <v>15</v>
       </c>
@@ -8498,10 +8698,12 @@
       </c>
       <c r="E7" s="3">
         <f t="shared" si="1"/>
-        <v>1.9607843137254902E-2</v>
+        <v>7.9365079365079378E-3</v>
       </c>
       <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
+      <c r="G7" s="3">
+        <v>0.2</v>
+      </c>
       <c r="H7" s="14" t="s">
         <v>13</v>
       </c>
@@ -8559,7 +8761,7 @@
       </c>
       <c r="E10" s="18">
         <f>$G$3/(2*B10+$G$3)</f>
-        <v>1.098901098901099E-2</v>
+        <v>4.4247787610619468E-3</v>
       </c>
       <c r="F10" s="19">
         <v>1196221.8700000001</v>
@@ -8592,7 +8794,7 @@
       </c>
       <c r="E11" s="18">
         <f t="shared" ref="E11:E14" si="3">$G$3/(2*B11+$G$3)</f>
-        <v>1.2345679012345678E-2</v>
+        <v>4.9751243781094526E-3</v>
       </c>
       <c r="F11" s="18"/>
       <c r="G11" s="18"/>
@@ -8621,7 +8823,7 @@
       </c>
       <c r="E12" s="18">
         <f t="shared" si="3"/>
-        <v>1.4084507042253521E-2</v>
+        <v>5.681818181818182E-3</v>
       </c>
       <c r="F12" s="18"/>
       <c r="G12" s="18"/>
@@ -8651,7 +8853,7 @@
       </c>
       <c r="E13" s="18">
         <f t="shared" si="3"/>
-        <v>1.6393442622950821E-2</v>
+        <v>6.6225165562913916E-3</v>
       </c>
       <c r="F13" s="18"/>
       <c r="G13" s="18"/>
@@ -8681,7 +8883,7 @@
       </c>
       <c r="E14" s="18">
         <f t="shared" si="3"/>
-        <v>1.9607843137254902E-2</v>
+        <v>7.9365079365079378E-3</v>
       </c>
       <c r="F14" s="18"/>
       <c r="G14" s="18"/>
@@ -8729,7 +8931,7 @@
       </c>
       <c r="E16" s="4">
         <f>$G$3/(2*B16+$G$3)</f>
-        <v>1.098901098901099E-2</v>
+        <v>4.4247787610619468E-3</v>
       </c>
       <c r="F16" s="20">
         <v>406813.75</v>
@@ -8762,7 +8964,7 @@
       </c>
       <c r="E17" s="4">
         <f t="shared" ref="E17:E20" si="5">$G$3/(2*B17+$G$3)</f>
-        <v>1.2345679012345678E-2</v>
+        <v>4.9751243781094526E-3</v>
       </c>
       <c r="F17" s="4"/>
       <c r="G17" s="4"/>
@@ -8791,7 +8993,7 @@
       </c>
       <c r="E18" s="4">
         <f t="shared" si="5"/>
-        <v>1.4084507042253521E-2</v>
+        <v>5.681818181818182E-3</v>
       </c>
       <c r="F18" s="4"/>
       <c r="G18" s="4"/>
@@ -8818,7 +9020,7 @@
       </c>
       <c r="E19" s="4">
         <f t="shared" si="5"/>
-        <v>1.6393442622950821E-2</v>
+        <v>6.6225165562913916E-3</v>
       </c>
       <c r="F19" s="4"/>
       <c r="G19" s="4"/>
@@ -8845,7 +9047,7 @@
       </c>
       <c r="E20" s="4">
         <f t="shared" si="5"/>
-        <v>1.9607843137254902E-2</v>
+        <v>7.9365079365079378E-3</v>
       </c>
       <c r="F20" s="4"/>
       <c r="G20" s="4"/>
@@ -8893,7 +9095,7 @@
       </c>
       <c r="E22" s="5">
         <f>$G$3/(2*B22+$G$3)</f>
-        <v>1.098901098901099E-2</v>
+        <v>4.4247787610619468E-3</v>
       </c>
       <c r="F22" s="21">
         <v>315667.90000000002</v>
@@ -8926,7 +9128,7 @@
       </c>
       <c r="E23" s="5">
         <f t="shared" ref="E23:E26" si="7">$G$3/(2*B23+$G$3)</f>
-        <v>1.2345679012345678E-2</v>
+        <v>4.9751243781094526E-3</v>
       </c>
       <c r="F23" s="5"/>
       <c r="G23" s="5"/>
@@ -8955,7 +9157,7 @@
       </c>
       <c r="E24" s="5">
         <f t="shared" si="7"/>
-        <v>1.4084507042253521E-2</v>
+        <v>5.681818181818182E-3</v>
       </c>
       <c r="F24" s="5"/>
       <c r="G24" s="5"/>
@@ -8982,7 +9184,7 @@
       </c>
       <c r="E25" s="5">
         <f t="shared" si="7"/>
-        <v>1.6393442622950821E-2</v>
+        <v>6.6225165562913916E-3</v>
       </c>
       <c r="F25" s="5"/>
       <c r="G25" s="5"/>
@@ -9009,7 +9211,7 @@
       </c>
       <c r="E26" s="5">
         <f t="shared" si="7"/>
-        <v>1.9607843137254902E-2</v>
+        <v>7.9365079365079378E-3</v>
       </c>
       <c r="F26" s="5"/>
       <c r="G26" s="5"/>
@@ -9065,7 +9267,7 @@
       </c>
       <c r="E33" s="4">
         <f>$G$3/(2*B33+$G$3)</f>
-        <v>1.098901098901099E-2</v>
+        <v>4.4247787610619468E-3</v>
       </c>
       <c r="F33" s="20">
         <v>22500</v>
@@ -9090,7 +9292,7 @@
       </c>
       <c r="E34" s="4">
         <f t="shared" ref="E34:E37" si="9">$G$3/(2*B34+$G$3)</f>
-        <v>1.2345679012345678E-2</v>
+        <v>4.9751243781094526E-3</v>
       </c>
       <c r="F34" s="29"/>
     </row>
@@ -9108,7 +9310,7 @@
       </c>
       <c r="E35" s="4">
         <f t="shared" si="9"/>
-        <v>1.4084507042253521E-2</v>
+        <v>5.681818181818182E-3</v>
       </c>
       <c r="F35" s="29"/>
       <c r="G35" s="22" t="s">
@@ -9129,7 +9331,7 @@
       </c>
       <c r="E36" s="4">
         <f t="shared" si="9"/>
-        <v>1.6393442622950821E-2</v>
+        <v>6.6225165562913916E-3</v>
       </c>
       <c r="F36" s="29"/>
     </row>
@@ -9147,7 +9349,7 @@
       </c>
       <c r="E37" s="4">
         <f t="shared" si="9"/>
-        <v>1.9607843137254902E-2</v>
+        <v>7.9365079365079378E-3</v>
       </c>
       <c r="F37" s="29"/>
     </row>
@@ -9194,7 +9396,7 @@
       </c>
       <c r="E40" s="3">
         <f>$G$3/(2*B40+$G$3)</f>
-        <v>1.098901098901099E-2</v>
+        <v>4.4247787610619468E-3</v>
       </c>
       <c r="F40" s="17">
         <v>22588.87</v>
@@ -9216,7 +9418,7 @@
       </c>
       <c r="E41" s="3">
         <f t="shared" ref="E41:E44" si="11">$G$3/(2*B41+$G$3)</f>
-        <v>1.2345679012345678E-2</v>
+        <v>4.9751243781094526E-3</v>
       </c>
       <c r="F41" s="30"/>
     </row>
@@ -9234,7 +9436,7 @@
       </c>
       <c r="E42" s="3">
         <f t="shared" si="11"/>
-        <v>1.4084507042253521E-2</v>
+        <v>5.681818181818182E-3</v>
       </c>
       <c r="F42" s="30"/>
       <c r="G42" s="22" t="s">
@@ -9255,7 +9457,7 @@
       </c>
       <c r="E43" s="3">
         <f t="shared" si="11"/>
-        <v>1.6393442622950821E-2</v>
+        <v>6.6225165562913916E-3</v>
       </c>
       <c r="F43" s="30"/>
     </row>
@@ -9273,7 +9475,7 @@
       </c>
       <c r="E44" s="3">
         <f t="shared" si="11"/>
-        <v>1.9607843137254902E-2</v>
+        <v>7.9365079365079378E-3</v>
       </c>
       <c r="F44" s="30"/>
     </row>
@@ -9311,8 +9513,8 @@
       <c r="B49" s="35">
         <v>120</v>
       </c>
-      <c r="C49" s="36">
-        <v>3736144.75</v>
+      <c r="C49" s="9">
+        <v>2239067</v>
       </c>
       <c r="D49" s="11"/>
       <c r="E49" s="11"/>
@@ -9330,8 +9532,8 @@
       <c r="B50" s="35">
         <v>100</v>
       </c>
-      <c r="C50" s="36">
-        <v>3704544.75</v>
+      <c r="C50" s="9">
+        <v>2223423</v>
       </c>
       <c r="D50" s="11"/>
       <c r="E50" s="11"/>
@@ -9349,8 +9551,8 @@
       <c r="B51" s="35">
         <v>80</v>
       </c>
-      <c r="C51" s="36">
-        <v>3612785.75</v>
+      <c r="C51" s="9">
+        <v>2190271</v>
       </c>
       <c r="D51" s="11"/>
       <c r="E51" s="11"/>
@@ -9368,8 +9570,8 @@
       <c r="B52" s="35">
         <v>60</v>
       </c>
-      <c r="C52" s="36">
-        <v>3554027.25</v>
+      <c r="C52" s="9">
+        <v>2155526</v>
       </c>
       <c r="D52" s="11"/>
       <c r="E52" s="11"/>
@@ -9387,8 +9589,8 @@
       <c r="B53" s="35">
         <v>40</v>
       </c>
-      <c r="C53" s="36">
-        <v>3529409</v>
+      <c r="C53" s="9">
+        <v>2140971</v>
       </c>
       <c r="D53" s="11"/>
       <c r="E53" s="11"/>
@@ -9406,8 +9608,8 @@
       <c r="B54" s="35">
         <v>60</v>
       </c>
-      <c r="C54" s="36">
-        <v>3541676.5</v>
+      <c r="C54" s="9">
+        <v>2157970</v>
       </c>
       <c r="D54" s="11"/>
       <c r="E54" s="11"/>
@@ -9425,8 +9627,8 @@
       <c r="B55" s="35">
         <v>80</v>
       </c>
-      <c r="C55" s="36">
-        <v>3621334.25</v>
+      <c r="C55" s="9">
+        <v>2220836</v>
       </c>
       <c r="D55" s="11"/>
       <c r="E55" s="11"/>
@@ -9444,8 +9646,8 @@
       <c r="B56" s="35">
         <v>100</v>
       </c>
-      <c r="C56" s="36">
-        <v>3677869.75</v>
+      <c r="C56" s="9">
+        <v>2231219</v>
       </c>
       <c r="D56" s="11"/>
       <c r="E56" s="11"/>
@@ -9463,8 +9665,8 @@
       <c r="B57" s="35">
         <v>120</v>
       </c>
-      <c r="C57" s="36">
-        <v>3700073</v>
+      <c r="C57" s="9">
+        <v>2231219</v>
       </c>
       <c r="D57" s="11"/>
       <c r="E57" s="11"/>
@@ -9482,8 +9684,8 @@
       <c r="B58" s="35">
         <v>100</v>
       </c>
-      <c r="C58" s="36">
-        <v>3669060.75</v>
+      <c r="C58" s="9">
+        <v>2226016</v>
       </c>
       <c r="D58" s="11"/>
       <c r="E58" s="11"/>
@@ -9493,8 +9695,8 @@
       <c r="B59" s="35">
         <v>80</v>
       </c>
-      <c r="C59" s="36">
-        <v>3634230.75</v>
+      <c r="C59" s="9">
+        <v>2210544</v>
       </c>
       <c r="D59" s="11"/>
       <c r="E59" s="11"/>
@@ -9504,8 +9706,8 @@
       <c r="B60" s="35">
         <v>60</v>
       </c>
-      <c r="C60" s="36">
-        <v>3578980.75</v>
+      <c r="C60" s="9">
+        <v>2145802</v>
       </c>
       <c r="D60" s="11"/>
       <c r="E60" s="11"/>
@@ -9515,325 +9717,365 @@
       <c r="B61" s="35">
         <v>40</v>
       </c>
-      <c r="C61" s="36">
-        <v>3465349</v>
+      <c r="C61" s="9">
+        <v>2133764</v>
       </c>
       <c r="D61" s="11"/>
       <c r="E61" s="11"/>
+    </row>
+    <row r="62" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B62" s="35">
+        <v>60</v>
+      </c>
+      <c r="C62" s="9">
+        <v>2140971</v>
+      </c>
     </row>
     <row r="63" spans="1:13" ht="23.4" x14ac:dyDescent="0.45">
       <c r="A63" s="31" t="s">
         <v>32</v>
       </c>
+      <c r="B63" s="35">
+        <v>80</v>
+      </c>
+      <c r="C63" s="9">
+        <v>2220836</v>
+      </c>
     </row>
     <row r="64" spans="1:13" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="A64" s="33" t="s">
+      <c r="A64" s="31">
+        <v>100</v>
+      </c>
+      <c r="B64" s="35">
+        <v>100</v>
+      </c>
+      <c r="C64" s="9">
+        <v>2228614</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" ht="23.4" x14ac:dyDescent="0.45">
+      <c r="A65" s="33" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A65" s="37"/>
-      <c r="B65" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="C65" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D65" s="10"/>
-      <c r="E65" s="10"/>
+      <c r="B65" s="35">
+        <v>120</v>
+      </c>
+      <c r="C65" s="9">
+        <v>2231219</v>
+      </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A66" s="37"/>
-      <c r="B66" s="38">
-        <v>120</v>
-      </c>
-      <c r="C66" s="19">
-        <v>23867.4</v>
-      </c>
-      <c r="D66" s="9"/>
-      <c r="E66" s="11"/>
+      <c r="A66" s="36"/>
+      <c r="B66" s="36" t="s">
+        <v>34</v>
+      </c>
+      <c r="C66" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="D66" s="10"/>
+      <c r="E66" s="10"/>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A67" s="37"/>
-      <c r="B67" s="38">
-        <v>100</v>
-      </c>
-      <c r="C67" s="19">
-        <v>24055.45</v>
+      <c r="A67" s="36"/>
+      <c r="B67" s="37">
+        <v>120</v>
+      </c>
+      <c r="C67" s="9">
+        <v>33307</v>
       </c>
       <c r="D67" s="9"/>
       <c r="E67" s="11"/>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A68" s="37"/>
-      <c r="B68" s="38">
-        <v>80</v>
-      </c>
-      <c r="C68" s="19">
-        <v>24244.9</v>
+      <c r="A68" s="36"/>
+      <c r="B68" s="37">
+        <v>100</v>
+      </c>
+      <c r="C68" s="9">
+        <v>32528</v>
       </c>
       <c r="D68" s="9"/>
       <c r="E68" s="11"/>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A69" s="37"/>
-      <c r="B69" s="38">
-        <v>60</v>
-      </c>
-      <c r="C69" s="19">
-        <v>24435.759999999998</v>
+      <c r="A69" s="36"/>
+      <c r="B69" s="37">
+        <v>80</v>
+      </c>
+      <c r="C69" s="9">
+        <v>31519</v>
       </c>
       <c r="D69" s="9"/>
       <c r="E69" s="11"/>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A70" s="37"/>
-      <c r="B70" s="38">
-        <v>40</v>
-      </c>
-      <c r="C70" s="19">
-        <v>24919.17</v>
+      <c r="A70" s="36"/>
+      <c r="B70" s="37">
+        <v>60</v>
+      </c>
+      <c r="C70" s="9">
+        <v>28463</v>
       </c>
       <c r="D70" s="9"/>
       <c r="E70" s="11"/>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A71" s="37"/>
-      <c r="B71" s="38">
-        <v>60</v>
-      </c>
-      <c r="C71" s="19">
-        <v>24531.72</v>
+      <c r="A71" s="36"/>
+      <c r="B71" s="37">
+        <v>40</v>
+      </c>
+      <c r="C71" s="9">
+        <v>27586</v>
       </c>
       <c r="D71" s="9"/>
       <c r="E71" s="11"/>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A72" s="37"/>
-      <c r="B72" s="38">
-        <v>80</v>
-      </c>
-      <c r="C72" s="19">
-        <v>24340.15</v>
+      <c r="A72" s="36"/>
+      <c r="B72" s="37">
+        <v>60</v>
+      </c>
+      <c r="C72" s="9">
+        <v>30905</v>
       </c>
       <c r="D72" s="9"/>
       <c r="E72" s="11"/>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A73" s="37"/>
-      <c r="B73" s="38">
-        <v>100</v>
-      </c>
-      <c r="C73" s="19">
-        <v>24150</v>
-      </c>
-      <c r="D73" s="12"/>
-      <c r="E73" s="11"/>
+      <c r="A73" s="36"/>
+      <c r="B73" s="37">
+        <v>80</v>
+      </c>
+      <c r="C73" s="9">
+        <v>32019</v>
+      </c>
+      <c r="D73" s="9"/>
+      <c r="E73" s="11" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A74" s="37"/>
-      <c r="B74" s="38">
-        <v>120</v>
-      </c>
-      <c r="C74" s="19">
-        <v>24055.45</v>
-      </c>
-      <c r="D74" s="9"/>
+      <c r="A74" s="36"/>
+      <c r="B74" s="37">
+        <v>100</v>
+      </c>
+      <c r="C74" s="9">
+        <v>32528</v>
+      </c>
+      <c r="D74" s="12"/>
       <c r="E74" s="11"/>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A75" s="37"/>
-      <c r="B75" s="38">
-        <v>100</v>
-      </c>
-      <c r="C75" s="19">
-        <v>24150</v>
+      <c r="A75" s="36"/>
+      <c r="B75" s="37">
+        <v>120</v>
+      </c>
+      <c r="C75" s="9">
+        <v>33705</v>
       </c>
       <c r="D75" s="9"/>
       <c r="E75" s="11"/>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A76" s="37"/>
-      <c r="B76" s="38">
-        <v>80</v>
-      </c>
-      <c r="C76" s="19">
-        <v>24244.9</v>
-      </c>
-      <c r="D76" s="11"/>
+      <c r="A76" s="36"/>
+      <c r="B76" s="37">
+        <v>100</v>
+      </c>
+      <c r="C76" s="9">
+        <v>31768</v>
+      </c>
+      <c r="D76" s="9"/>
       <c r="E76" s="11"/>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A77" s="37"/>
-      <c r="B77" s="38">
-        <v>60</v>
-      </c>
-      <c r="C77" s="19">
-        <v>24531.72</v>
+      <c r="A77" s="36"/>
+      <c r="B77" s="37">
+        <v>80</v>
+      </c>
+      <c r="C77" s="9">
+        <v>30905</v>
       </c>
       <c r="D77" s="11"/>
       <c r="E77" s="11"/>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A78" s="37"/>
-      <c r="B78" s="38">
-        <v>40</v>
-      </c>
-      <c r="C78" s="19">
-        <v>24919.17</v>
+      <c r="A78" s="36"/>
+      <c r="B78" s="37">
+        <v>60</v>
+      </c>
+      <c r="C78" s="9">
+        <v>29484</v>
       </c>
       <c r="D78" s="11"/>
       <c r="E78" s="11"/>
     </row>
-    <row r="91" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A91" s="2"/>
-      <c r="B91" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C91" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D91" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E91" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="F91" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="G91" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H91" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="I91" s="8" t="s">
-        <v>11</v>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A79" s="36"/>
+      <c r="B79" s="37">
+        <v>40</v>
+      </c>
+      <c r="C79" s="9">
+        <v>28242</v>
+      </c>
+      <c r="D79" s="11"/>
+      <c r="E79" s="11"/>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B80" s="37">
+        <v>60</v>
+      </c>
+      <c r="C80" s="9">
+        <v>30905</v>
+      </c>
+    </row>
+    <row r="81" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B81" s="37">
+        <v>80</v>
+      </c>
+      <c r="C81" s="9">
+        <v>31643</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B82" s="37">
+        <v>100</v>
+      </c>
+      <c r="C82" s="9">
+        <v>32272</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B83" s="37">
+        <v>120</v>
+      </c>
+      <c r="C83" s="9">
+        <v>33705</v>
       </c>
     </row>
     <row r="92" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A92" s="3"/>
-      <c r="B92" s="3"/>
-      <c r="C92" s="3"/>
-      <c r="D92" s="3">
+      <c r="A92" s="2"/>
+      <c r="B92" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E92" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F92" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="E92" s="3">
-        <v>0</v>
-      </c>
-      <c r="F92" s="3"/>
-      <c r="G92" s="3"/>
-      <c r="H92" s="8"/>
-      <c r="I92" s="8"/>
+      <c r="G92" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H92" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="I92" s="8" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="93" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A93" s="3"/>
-      <c r="B93" s="3">
-        <v>22.5</v>
-      </c>
-      <c r="C93" s="17">
-        <v>1300367.1200000001</v>
-      </c>
+      <c r="B93" s="3"/>
+      <c r="C93" s="3"/>
       <c r="D93" s="3">
-        <f>(C93-$F$93)/$F$93</f>
-        <v>0.35639116143408311</v>
+        <v>0</v>
       </c>
       <c r="E93" s="3">
-        <f>$G$3/(2*B93+$G$3)</f>
-        <v>1.098901098901099E-2</v>
-      </c>
-      <c r="F93" s="17">
-        <v>958696.25</v>
-      </c>
-      <c r="G93" s="3">
-        <v>0.5</v>
-      </c>
-      <c r="H93" s="25" t="s">
-        <v>40</v>
-      </c>
-      <c r="I93" s="25">
-        <v>2859</v>
-      </c>
-      <c r="J93" s="9">
-        <v>11843</v>
-      </c>
-      <c r="K93" s="9" t="s">
-        <v>41</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F93" s="3"/>
+      <c r="G93" s="3"/>
+      <c r="H93" s="8"/>
+      <c r="I93" s="8"/>
     </row>
     <row r="94" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A94" s="3"/>
       <c r="B94" s="3">
-        <v>20</v>
+        <v>22.5</v>
       </c>
       <c r="C94" s="17">
-        <v>1376309.87</v>
+        <v>1300367.1200000001</v>
       </c>
       <c r="D94" s="3">
-        <f t="shared" ref="D94:D97" si="12">(C94-$F$93)/$F$93</f>
-        <v>0.43560577190116279</v>
+        <f>(C94-$F$94)/$F$94</f>
+        <v>0.35639116143408311</v>
       </c>
       <c r="E94" s="3">
-        <f t="shared" ref="E94:E97" si="13">$G$3/(2*B94+$G$3)</f>
-        <v>1.2345679012345678E-2</v>
-      </c>
-      <c r="F94" s="3"/>
-      <c r="G94" s="3"/>
+        <f>$G$3/(2*B94+$G$3)</f>
+        <v>4.4247787610619468E-3</v>
+      </c>
+      <c r="F94" s="17">
+        <v>958696.25</v>
+      </c>
+      <c r="G94" s="3">
+        <v>0.5</v>
+      </c>
       <c r="H94" s="25" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="I94" s="25">
         <v>2859</v>
       </c>
+      <c r="J94" s="9">
+        <v>11843</v>
+      </c>
+      <c r="K94" s="9" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="95" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A95" s="3" t="s">
-        <v>4</v>
-      </c>
+      <c r="A95" s="3"/>
       <c r="B95" s="3">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="C95" s="17">
-        <v>1399533.5</v>
+        <v>1376309.87</v>
       </c>
       <c r="D95" s="3">
-        <f t="shared" si="12"/>
-        <v>0.45982995135320492</v>
+        <f t="shared" ref="D95:D98" si="12">(C95-$F$94)/$F$94</f>
+        <v>0.43560577190116279</v>
       </c>
       <c r="E95" s="3">
-        <f t="shared" si="13"/>
-        <v>1.4084507042253521E-2</v>
+        <f t="shared" ref="E95:E98" si="13">$G$3/(2*B95+$G$3)</f>
+        <v>4.9751243781094526E-3</v>
       </c>
       <c r="F95" s="3"/>
       <c r="G95" s="3"/>
       <c r="H95" s="25" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I95" s="25">
         <v>2859</v>
       </c>
     </row>
     <row r="96" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A96" s="3"/>
+      <c r="A96" s="3" t="s">
+        <v>4</v>
+      </c>
       <c r="B96" s="3">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="C96" s="17">
-        <v>1476373.37</v>
+        <v>1399533.5</v>
       </c>
       <c r="D96" s="3">
         <f t="shared" si="12"/>
-        <v>0.53998033266532552</v>
+        <v>0.45982995135320492</v>
       </c>
       <c r="E96" s="3">
         <f t="shared" si="13"/>
-        <v>1.6393442622950821E-2</v>
+        <v>5.681818181818182E-3</v>
       </c>
       <c r="F96" s="3"/>
       <c r="G96" s="3"/>
       <c r="H96" s="25" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I96" s="25">
         <v>2859</v>
@@ -9842,112 +10084,110 @@
     <row r="97" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A97" s="3"/>
       <c r="B97" s="3">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="C97" s="17">
-        <v>1567259.5</v>
+        <v>1476373.37</v>
       </c>
       <c r="D97" s="3">
         <f t="shared" si="12"/>
-        <v>0.63478213250547288</v>
+        <v>0.53998033266532552</v>
       </c>
       <c r="E97" s="3">
         <f t="shared" si="13"/>
-        <v>1.9607843137254902E-2</v>
+        <v>6.6225165562913916E-3</v>
       </c>
       <c r="F97" s="3"/>
       <c r="G97" s="3"/>
       <c r="H97" s="25" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I97" s="25">
         <v>2859</v>
       </c>
     </row>
     <row r="98" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A98" s="18"/>
-      <c r="B98" s="18"/>
-      <c r="C98" s="19"/>
-      <c r="D98" s="18">
-        <v>0</v>
-      </c>
-      <c r="E98" s="18">
-        <v>0</v>
-      </c>
-      <c r="F98" s="18"/>
-      <c r="G98" s="18"/>
-      <c r="H98" s="25"/>
-      <c r="I98" s="25"/>
+      <c r="A98" s="3"/>
+      <c r="B98" s="3">
+        <v>12.5</v>
+      </c>
+      <c r="C98" s="17">
+        <v>1567259.5</v>
+      </c>
+      <c r="D98" s="3">
+        <f t="shared" si="12"/>
+        <v>0.63478213250547288</v>
+      </c>
+      <c r="E98" s="3">
+        <f t="shared" si="13"/>
+        <v>7.9365079365079378E-3</v>
+      </c>
+      <c r="F98" s="3"/>
+      <c r="G98" s="3"/>
+      <c r="H98" s="25" t="s">
+        <v>39</v>
+      </c>
+      <c r="I98" s="25">
+        <v>2859</v>
+      </c>
     </row>
     <row r="99" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A99" s="18"/>
-      <c r="B99" s="18">
-        <v>22.5</v>
-      </c>
-      <c r="C99" s="19">
-        <v>1297911.8700000001</v>
-      </c>
+      <c r="B99" s="18"/>
+      <c r="C99" s="19"/>
       <c r="D99" s="18">
-        <f>(C99-$F$99)/$F$99</f>
-        <v>0.23635897203469025</v>
+        <v>0</v>
       </c>
       <c r="E99" s="18">
-        <f>$G$3/(2*B99+$G$3)</f>
-        <v>1.098901098901099E-2</v>
-      </c>
-      <c r="F99" s="19">
-        <v>1049785.6200000001</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F99" s="18"/>
       <c r="G99" s="18"/>
-      <c r="H99" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="I99" s="25">
-        <v>11843</v>
-      </c>
+      <c r="H99" s="25"/>
+      <c r="I99" s="25"/>
     </row>
     <row r="100" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A100" s="18"/>
       <c r="B100" s="18">
-        <v>20</v>
+        <v>22.5</v>
       </c>
       <c r="C100" s="19">
-        <v>1344497</v>
+        <v>1297911.8700000001</v>
       </c>
       <c r="D100" s="18">
-        <f t="shared" ref="D100:D103" si="14">(C100-$F$99)/$F$99</f>
-        <v>0.28073482279172374</v>
+        <f>(C100-$F$100)/$F$100</f>
+        <v>0.23635897203469025</v>
       </c>
       <c r="E100" s="18">
-        <f t="shared" ref="E100:E103" si="15">$G$3/(2*B100+$G$3)</f>
-        <v>1.2345679012345678E-2</v>
-      </c>
-      <c r="F100" s="18"/>
+        <f>$G$3/(2*B100+$G$3)</f>
+        <v>4.4247787610619468E-3</v>
+      </c>
+      <c r="F100" s="19">
+        <v>1049785.6200000001</v>
+      </c>
       <c r="G100" s="18"/>
       <c r="H100" s="26" t="s">
-        <v>18</v>
-      </c>
-      <c r="I100" s="26">
-        <v>7156</v>
+        <v>17</v>
+      </c>
+      <c r="I100" s="25">
+        <v>11843</v>
       </c>
     </row>
     <row r="101" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A101" s="18" t="s">
-        <v>5</v>
-      </c>
+      <c r="A101" s="18"/>
       <c r="B101" s="18">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="C101" s="19">
-        <v>1398428</v>
+        <v>1344497</v>
       </c>
       <c r="D101" s="18">
-        <f t="shared" si="14"/>
-        <v>0.33210816890404715</v>
+        <f t="shared" ref="D101:D104" si="14">(C101-$F$100)/$F$100</f>
+        <v>0.28073482279172374</v>
       </c>
       <c r="E101" s="18">
-        <f t="shared" si="15"/>
-        <v>1.4084507042253521E-2</v>
+        <f t="shared" ref="E101:E104" si="15">$G$3/(2*B101+$G$3)</f>
+        <v>4.9751243781094526E-3</v>
       </c>
       <c r="F101" s="18"/>
       <c r="G101" s="18"/>
@@ -9955,181 +10195,183 @@
         <v>18</v>
       </c>
       <c r="I101" s="26">
-        <v>6765</v>
+        <v>7156</v>
       </c>
     </row>
     <row r="102" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A102" s="18"/>
+      <c r="A102" s="18" t="s">
+        <v>5</v>
+      </c>
       <c r="B102" s="18">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="C102" s="19">
-        <v>1516433.37</v>
+        <v>1398428</v>
       </c>
       <c r="D102" s="18">
         <f t="shared" si="14"/>
-        <v>0.44451718628037595</v>
+        <v>0.33210816890404715</v>
       </c>
       <c r="E102" s="18">
         <f t="shared" si="15"/>
-        <v>1.6393442622950821E-2</v>
+        <v>5.681818181818182E-3</v>
       </c>
       <c r="F102" s="18"/>
       <c r="G102" s="18"/>
       <c r="H102" s="26" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I102" s="26">
-        <v>8328</v>
+        <v>6765</v>
       </c>
     </row>
-    <row r="103" spans="1:10" ht="25.8" x14ac:dyDescent="0.5">
+    <row r="103" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A103" s="18"/>
       <c r="B103" s="18">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="C103" s="19">
-        <v>1590882.87</v>
+        <v>1516433.37</v>
       </c>
       <c r="D103" s="18">
         <f t="shared" si="14"/>
-        <v>0.51543595158028543</v>
+        <v>0.44451718628037595</v>
       </c>
       <c r="E103" s="18">
         <f t="shared" si="15"/>
-        <v>1.9607843137254902E-2</v>
+        <v>6.6225165562913916E-3</v>
       </c>
       <c r="F103" s="18"/>
       <c r="G103" s="18"/>
       <c r="H103" s="26" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I103" s="26">
         <v>8328</v>
       </c>
-      <c r="J103" s="27" t="s">
+    </row>
+    <row r="104" spans="1:10" ht="25.8" x14ac:dyDescent="0.5">
+      <c r="A104" s="18"/>
+      <c r="B104" s="18">
+        <v>12.5</v>
+      </c>
+      <c r="C104" s="19">
+        <v>1590882.87</v>
+      </c>
+      <c r="D104" s="18">
+        <f t="shared" si="14"/>
+        <v>0.51543595158028543</v>
+      </c>
+      <c r="E104" s="18">
+        <f t="shared" si="15"/>
+        <v>7.9365079365079378E-3</v>
+      </c>
+      <c r="F104" s="18"/>
+      <c r="G104" s="18"/>
+      <c r="H104" s="26" t="s">
+        <v>20</v>
+      </c>
+      <c r="I104" s="26">
+        <v>8328</v>
+      </c>
+      <c r="J104" s="27" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="104" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A104" s="23">
+    <row r="105" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A105" s="23">
         <v>0</v>
       </c>
-      <c r="B104" s="23"/>
-      <c r="C104" s="24"/>
-      <c r="D104" s="23">
+      <c r="B105" s="23"/>
+      <c r="C105" s="24"/>
+      <c r="D105" s="23">
         <v>0</v>
       </c>
-      <c r="E104" s="23">
+      <c r="E105" s="23">
         <v>0</v>
       </c>
-      <c r="F104" s="23"/>
-      <c r="G104" s="23"/>
-      <c r="H104" s="26"/>
-      <c r="I104" s="26"/>
+      <c r="F105" s="23"/>
+      <c r="G105" s="23"/>
+      <c r="H105" s="26"/>
+      <c r="I105" s="26"/>
     </row>
-    <row r="105" spans="1:10" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="A105" s="23"/>
-      <c r="B105" s="23">
-        <v>22.5</v>
-      </c>
-      <c r="C105" s="24">
-        <v>565121.43000000005</v>
-      </c>
-      <c r="D105" s="23">
-        <f>(C105-$F$105)/$F$105</f>
-        <v>0.20578402327409914</v>
-      </c>
-      <c r="E105" s="23">
-        <f>$G$3/(2*B105+$G$3)</f>
-        <v>1.098901098901099E-2</v>
-      </c>
-      <c r="F105" s="24">
-        <v>468675.5</v>
-      </c>
-      <c r="G105" s="23"/>
-      <c r="H105" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="I105" s="25">
-        <v>24343</v>
-      </c>
-      <c r="J105" s="22" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="106" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:10" ht="23.4" x14ac:dyDescent="0.45">
       <c r="A106" s="23"/>
       <c r="B106" s="23">
-        <v>20</v>
+        <v>22.5</v>
       </c>
       <c r="C106" s="24">
-        <v>585187.56000000006</v>
+        <v>565121.43000000005</v>
       </c>
       <c r="D106" s="23">
-        <f t="shared" ref="D106:D109" si="16">(C106-$F$105)/$F$105</f>
-        <v>0.24859857193303267</v>
+        <f>(C106-$F$106)/$F$106</f>
+        <v>0.20578402327409914</v>
       </c>
       <c r="E106" s="23">
-        <f t="shared" ref="E106:E109" si="17">$G$3/(2*B106+$G$3)</f>
-        <v>1.2345679012345678E-2</v>
-      </c>
-      <c r="F106" s="23"/>
+        <f>$G$3/(2*B106+$G$3)</f>
+        <v>4.4247787610619468E-3</v>
+      </c>
+      <c r="F106" s="24">
+        <v>468675.5</v>
+      </c>
       <c r="G106" s="23"/>
       <c r="H106" s="26" t="s">
-        <v>23</v>
-      </c>
-      <c r="I106" s="26">
-        <v>23171</v>
+        <v>22</v>
+      </c>
+      <c r="I106" s="25">
+        <v>24343</v>
+      </c>
+      <c r="J106" s="22" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="107" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A107" s="23" t="s">
-        <v>6</v>
-      </c>
+      <c r="A107" s="23"/>
       <c r="B107" s="23">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="C107" s="24">
-        <v>605813.68000000005</v>
+        <v>585187.56000000006</v>
       </c>
       <c r="D107" s="23">
-        <f t="shared" si="16"/>
-        <v>0.29260795582444582</v>
+        <f t="shared" ref="D107:D110" si="16">(C107-$F$106)/$F$106</f>
+        <v>0.24859857193303267</v>
       </c>
       <c r="E107" s="23">
-        <f t="shared" si="17"/>
-        <v>1.4084507042253521E-2</v>
+        <f t="shared" ref="E107:E110" si="17">$G$3/(2*B107+$G$3)</f>
+        <v>4.9751243781094526E-3</v>
       </c>
       <c r="F107" s="23"/>
       <c r="G107" s="23"/>
       <c r="H107" s="26" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I107" s="26">
         <v>23171</v>
       </c>
     </row>
     <row r="108" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A108" s="23"/>
+      <c r="A108" s="23" t="s">
+        <v>6</v>
+      </c>
       <c r="B108" s="23">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="C108" s="24">
-        <v>626764.93000000005</v>
+        <v>605813.68000000005</v>
       </c>
       <c r="D108" s="23">
         <f t="shared" si="16"/>
-        <v>0.33731106063790417</v>
+        <v>0.29260795582444582</v>
       </c>
       <c r="E108" s="23">
         <f t="shared" si="17"/>
-        <v>1.6393442622950821E-2</v>
+        <v>5.681818181818182E-3</v>
       </c>
       <c r="F108" s="23"/>
       <c r="G108" s="23"/>
       <c r="H108" s="26" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="I108" s="26">
         <v>23171</v>
@@ -10138,144 +10380,144 @@
     <row r="109" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A109" s="23"/>
       <c r="B109" s="23">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="C109" s="24">
-        <v>656193.5</v>
+        <v>626764.93000000005</v>
       </c>
       <c r="D109" s="23">
         <f t="shared" si="16"/>
-        <v>0.40010198954287135</v>
+        <v>0.33731106063790417</v>
       </c>
       <c r="E109" s="23">
         <f t="shared" si="17"/>
-        <v>1.9607843137254902E-2</v>
+        <v>6.6225165562913916E-3</v>
       </c>
       <c r="F109" s="23"/>
       <c r="G109" s="23"/>
       <c r="H109" s="26" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I109" s="26">
-        <v>20828</v>
+        <v>23171</v>
       </c>
     </row>
     <row r="110" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A110" s="5">
-        <v>0</v>
-      </c>
-      <c r="B110" s="5"/>
-      <c r="C110" s="21"/>
-      <c r="D110" s="5">
-        <v>0</v>
-      </c>
-      <c r="E110" s="5">
-        <v>0</v>
-      </c>
-      <c r="F110" s="5"/>
-      <c r="G110" s="5"/>
-      <c r="H110" s="26"/>
-      <c r="I110" s="26"/>
+      <c r="A110" s="23"/>
+      <c r="B110" s="23">
+        <v>12.5</v>
+      </c>
+      <c r="C110" s="24">
+        <v>656193.5</v>
+      </c>
+      <c r="D110" s="23">
+        <f t="shared" si="16"/>
+        <v>0.40010198954287135</v>
+      </c>
+      <c r="E110" s="23">
+        <f t="shared" si="17"/>
+        <v>7.9365079365079378E-3</v>
+      </c>
+      <c r="F110" s="23"/>
+      <c r="G110" s="23"/>
+      <c r="H110" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="I110" s="26">
+        <v>20828</v>
+      </c>
     </row>
     <row r="111" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A111" s="5"/>
-      <c r="B111" s="5">
-        <v>22.5</v>
-      </c>
-      <c r="C111" s="21">
-        <v>1119915</v>
-      </c>
+      <c r="A111" s="5">
+        <v>0</v>
+      </c>
+      <c r="B111" s="5"/>
+      <c r="C111" s="21"/>
       <c r="D111" s="5">
-        <f>(C111-$F$111)/$F$111</f>
-        <v>0.18047670107613362</v>
+        <v>0</v>
       </c>
       <c r="E111" s="5">
-        <f>$G$3/(2*B111+$G$3)</f>
-        <v>1.098901098901099E-2</v>
-      </c>
-      <c r="F111" s="21">
-        <v>948697.25</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F111" s="5"/>
       <c r="G111" s="5"/>
-      <c r="H111" s="26" t="s">
-        <v>27</v>
-      </c>
-      <c r="I111" s="25">
-        <v>12625</v>
-      </c>
+      <c r="H111" s="26"/>
+      <c r="I111" s="26"/>
     </row>
     <row r="112" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A112" s="5"/>
       <c r="B112" s="5">
-        <v>20</v>
+        <v>22.5</v>
       </c>
       <c r="C112" s="21">
-        <v>1150493.1200000001</v>
+        <v>1119915</v>
       </c>
       <c r="D112" s="5">
-        <f t="shared" ref="D112:D115" si="18">(C112-$F$111)/$F$111</f>
-        <v>0.21270839564465915</v>
+        <f>(C112-$F$112)/$F$112</f>
+        <v>0.18047670107613362</v>
       </c>
       <c r="E112" s="5">
-        <f t="shared" ref="E112:E115" si="19">$G$3/(2*B112+$G$3)</f>
-        <v>1.2345679012345678E-2</v>
-      </c>
-      <c r="F112" s="5"/>
+        <f>$G$3/(2*B112+$G$3)</f>
+        <v>4.4247787610619468E-3</v>
+      </c>
+      <c r="F112" s="21">
+        <v>948697.25</v>
+      </c>
       <c r="G112" s="5"/>
       <c r="H112" s="26" t="s">
-        <v>28</v>
-      </c>
-      <c r="I112" s="26">
-        <v>25515</v>
+        <v>27</v>
+      </c>
+      <c r="I112" s="25">
+        <v>12625</v>
       </c>
     </row>
     <row r="113" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A113" s="5" t="s">
-        <v>7</v>
-      </c>
+      <c r="A113" s="5"/>
       <c r="B113" s="5">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="C113" s="21">
-        <v>1188146.5</v>
+        <v>1150493.1200000001</v>
       </c>
       <c r="D113" s="5">
-        <f t="shared" si="18"/>
-        <v>0.25239795941223608</v>
+        <f t="shared" ref="D113:D116" si="18">(C113-$F$112)/$F$112</f>
+        <v>0.21270839564465915</v>
       </c>
       <c r="E113" s="5">
-        <f t="shared" si="19"/>
-        <v>1.4084507042253521E-2</v>
+        <f t="shared" ref="E113:E116" si="19">$G$3/(2*B113+$G$3)</f>
+        <v>4.9751243781094526E-3</v>
       </c>
       <c r="F113" s="5"/>
       <c r="G113" s="5"/>
       <c r="H113" s="26" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I113" s="26">
-        <v>22781</v>
+        <v>25515</v>
       </c>
     </row>
     <row r="114" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A114" s="5"/>
+      <c r="A114" s="5" t="s">
+        <v>7</v>
+      </c>
       <c r="B114" s="5">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="C114" s="21">
-        <v>1234031</v>
+        <v>1188146.5</v>
       </c>
       <c r="D114" s="5">
         <f t="shared" si="18"/>
-        <v>0.30076375787955534</v>
+        <v>0.25239795941223608</v>
       </c>
       <c r="E114" s="5">
         <f t="shared" si="19"/>
-        <v>1.6393442622950821E-2</v>
+        <v>5.681818181818182E-3</v>
       </c>
       <c r="F114" s="5"/>
       <c r="G114" s="5"/>
       <c r="H114" s="26" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I114" s="26">
         <v>22781</v>
@@ -10284,25 +10526,50 @@
     <row r="115" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A115" s="5"/>
       <c r="B115" s="5">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="C115" s="21">
-        <v>1313982.6200000001</v>
+        <v>1234031</v>
       </c>
       <c r="D115" s="5">
         <f t="shared" si="18"/>
-        <v>0.38503892574791393</v>
+        <v>0.30076375787955534</v>
       </c>
       <c r="E115" s="5">
         <f t="shared" si="19"/>
-        <v>1.9607843137254902E-2</v>
+        <v>6.6225165562913916E-3</v>
       </c>
       <c r="F115" s="5"/>
       <c r="G115" s="5"/>
       <c r="H115" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I115" s="26">
+        <v>22781</v>
+      </c>
+    </row>
+    <row r="116" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A116" s="5"/>
+      <c r="B116" s="5">
+        <v>12.5</v>
+      </c>
+      <c r="C116" s="21">
+        <v>1313982.6200000001</v>
+      </c>
+      <c r="D116" s="5">
+        <f t="shared" si="18"/>
+        <v>0.38503892574791393</v>
+      </c>
+      <c r="E116" s="5">
+        <f t="shared" si="19"/>
+        <v>7.9365079365079378E-3</v>
+      </c>
+      <c r="F116" s="5"/>
+      <c r="G116" s="5"/>
+      <c r="H116" s="26" t="s">
         <v>31</v>
       </c>
-      <c r="I115" s="26">
+      <c r="I116" s="26">
         <v>21218</v>
       </c>
     </row>
